--- a/public/templates/peraturan.xlsx
+++ b/public/templates/peraturan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KERJA PRAKTIK 2025\Matriks Klaster\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT WEB RANDIKA\sipandakabulan-new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0A505DD-CDF6-4F06-8B36-903B446AF8ED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AC20CA-44BA-4ED0-8427-D275E363A756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{0224711C-8D23-412A-AA75-A8035D14BD66}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0224711C-8D23-412A-AA75-A8035D14BD66}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -164,18 +164,6 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -189,6 +177,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -506,341 +506,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A13B2700-F883-4512-917D-14818C5B7434}">
   <dimension ref="A4:Q16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2">
-        <v>2021</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2">
-        <v>2022</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7">
+        <v>2024</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7">
+        <v>2025</v>
+      </c>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-    </row>
-    <row r="7" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-    </row>
-    <row r="8" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-    </row>
-    <row r="9" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-    </row>
-    <row r="10" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="4">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-    </row>
-    <row r="11" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="4">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
         <v>6</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-    </row>
-    <row r="12" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
         <v>7</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-    </row>
-    <row r="13" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="4">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
         <v>8</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-    </row>
-    <row r="14" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="4">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
         <v>9</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-    </row>
-    <row r="16" spans="1:17" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:G5"/>
+    <mergeCell ref="H4:Q4"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="M5:Q5"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="M7:Q7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="M9:Q9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="H10:L10"/>
+    <mergeCell ref="M10:Q10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="H11:L11"/>
+    <mergeCell ref="M11:Q11"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="M14:Q14"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="H15:L15"/>
     <mergeCell ref="M15:Q15"/>
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="H16:L16"/>
     <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="M13:Q13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="M14:Q14"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="H11:L11"/>
-    <mergeCell ref="M11:Q11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="H9:L9"/>
-    <mergeCell ref="M9:Q9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="H10:L10"/>
-    <mergeCell ref="M10:Q10"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="M7:Q7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="H8:L8"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:G5"/>
-    <mergeCell ref="H4:Q4"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="M5:Q5"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
